--- a/Консп.xlsx
+++ b/Консп.xlsx
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1155" uniqueCount="1121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1184" uniqueCount="1150">
   <si>
     <t>&lt;a&gt;</t>
   </si>
@@ -6613,12 +6613,151 @@
     <t xml:space="preserve">    Зупиняє "спливання" події так само, як event.stopPropagation().
     Також зупиняє виконання всіх інших обробників подій, які слухають цю ж подію на даному елементі, навіть якщо вони були зареєстровані перед цим.</t>
   </si>
+  <si>
+    <t>JSON.stringify(value)</t>
+  </si>
+  <si>
+    <t>приймає значення і перетворює його у JSON. Значенням може бути число, буль, null, масив, об'єкт.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">console.log(JSON.parse("5")); // 5
+console.log(JSON.parse("false")); // false
+console.log(JSON.parse("null")); // null
+</t>
+  </si>
+  <si>
+    <t>Щоб отримати з JSON валідне JavaScript значення, його необхідно розпарсити (parse). Це операція зворотня перетворенню JavaScript об'єкта в json</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">JSON - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>сучасний текстовий формат зберігання й передачі структурованих даних у текстовій формі</t>
+    </r>
+  </si>
+  <si>
+    <t>setItem(key, value)</t>
+  </si>
+  <si>
+    <t>додамо пару ключ-значення до локального сховища за допомогою методу setItem(key, value), доступного в об’єкті localStorage:</t>
+  </si>
+  <si>
+    <t>localStorage.setItem("ui-theme", "light");</t>
+  </si>
+  <si>
+    <t>getItem(key)</t>
+  </si>
+  <si>
+    <t>Метод getItem(key) дозволяє зчитати зі сховища запис із ключем key і повертає його значення у JSON форматі.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">const savedTheme = localStorage.getItem("ui-theme"); 
+console.log(savedTheme); // "light"
+</t>
+  </si>
+  <si>
+    <t>removeItem(key)</t>
+  </si>
+  <si>
+    <t>Метод removeItem(key) видаляє зі сховища існуючий запис з ключем key. В результаті своєї роботи він не повертає значення.</t>
+  </si>
+  <si>
+    <t>localStorage.setItem("ui-theme", "dark");
+console.log(localStorage.getItem("ui-theme")); // "dark"
+localStorage.removeItem("ui-theme");
+console.log(localStorage.getItem("ui-theme")); // null</t>
+  </si>
+  <si>
+    <t>JSON.parse(value)</t>
+  </si>
+  <si>
+    <t>delete object.key</t>
+  </si>
+  <si>
+    <t>delete user.age;</t>
+  </si>
+  <si>
+    <t>видаляє властивість і її значення</t>
+  </si>
+  <si>
+    <t>перевіряє існування ключа</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">"propertyName" </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>in</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> object</t>
+    </r>
+  </si>
+  <si>
+    <t>const user = {
+    email: undefined
+};
+console.log("email" in user); // true</t>
+  </si>
+  <si>
+    <t>obj.hasOwnProperty(key)</t>
+  </si>
+  <si>
+    <t>Цей метод повертає true, якщо властивість з іменем key належить об'єкту obj</t>
+  </si>
+  <si>
+    <t>Object.entries(obj)</t>
+  </si>
+  <si>
+    <t>const person = { name: "Igor", age: 25, profession: "manager"};          const result = Object.entries(person);
+console.log(result);
+//[["name", "Igor"], ["age", 25], ["profession", "manager"]]</t>
+  </si>
+  <si>
+    <t>Object.fromEntries(obj)</t>
+  </si>
+  <si>
+    <t>перетворює об'єкт в масив масивів</t>
+  </si>
+  <si>
+    <t>перетворює масив масивів в  об'єкт</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[["name", "John"], ["age", 25], ["address", "123 Street"]]                      const result = Object.fromEntries(person);
+console.log(result);
+{name: "John", age: 25, address: "123 Street"}  </t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="14">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -6723,6 +6862,14 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="204"/>
@@ -7038,7 +7185,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="98">
+  <cellXfs count="99">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -7214,17 +7361,29 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -7235,37 +7394,25 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -7277,17 +7424,20 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -8846,9 +8996,9 @@
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="76"/>
-      <c r="B3" s="76"/>
-      <c r="C3" s="76"/>
+      <c r="A3" s="78"/>
+      <c r="B3" s="78"/>
+      <c r="C3" s="78"/>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="72" t="s">
@@ -8979,16 +9129,16 @@
       </c>
     </row>
     <row r="16" spans="1:3">
-      <c r="A16" s="79"/>
-      <c r="B16" s="79"/>
-      <c r="C16" s="79"/>
+      <c r="A16" s="83"/>
+      <c r="B16" s="83"/>
+      <c r="C16" s="83"/>
     </row>
     <row r="17" spans="1:3">
-      <c r="A17" s="77" t="s">
+      <c r="A17" s="81" t="s">
         <v>523</v>
       </c>
-      <c r="B17" s="77"/>
-      <c r="C17" s="77"/>
+      <c r="B17" s="81"/>
+      <c r="C17" s="81"/>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="25" t="s">
@@ -9062,11 +9212,11 @@
       </c>
     </row>
     <row r="26" spans="1:3">
-      <c r="A26" s="77" t="s">
+      <c r="A26" s="81" t="s">
         <v>546</v>
       </c>
-      <c r="B26" s="77"/>
-      <c r="C26" s="77"/>
+      <c r="B26" s="81"/>
+      <c r="C26" s="81"/>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="28" t="s">
@@ -9131,28 +9281,28 @@
       <c r="C33" s="72"/>
     </row>
     <row r="34" spans="1:3">
-      <c r="A34" s="78" t="s">
+      <c r="A34" s="82" t="s">
         <v>496</v>
       </c>
-      <c r="B34" s="78"/>
+      <c r="B34" s="82"/>
       <c r="C34" s="28" t="s">
         <v>547</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="15.75">
-      <c r="A35" s="75" t="s">
+      <c r="A35" s="74" t="s">
         <v>548</v>
       </c>
-      <c r="B35" s="75"/>
+      <c r="B35" s="74"/>
       <c r="C35" s="24" t="s">
         <v>549</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="15.75">
-      <c r="A36" s="75" t="s">
+      <c r="A36" s="74" t="s">
         <v>550</v>
       </c>
-      <c r="B36" s="75"/>
+      <c r="B36" s="74"/>
       <c r="C36" s="24" t="s">
         <v>551</v>
       </c>
@@ -9472,11 +9622,11 @@
       </c>
     </row>
     <row r="78" spans="1:3">
-      <c r="A78" s="83" t="s">
+      <c r="A78" s="73" t="s">
         <v>569</v>
       </c>
-      <c r="B78" s="83"/>
-      <c r="C78" s="83"/>
+      <c r="B78" s="73"/>
+      <c r="C78" s="73"/>
     </row>
     <row r="79" spans="1:3">
       <c r="A79" s="35" t="s">
@@ -9509,11 +9659,11 @@
       </c>
     </row>
     <row r="83" spans="1:3">
-      <c r="A83" s="83" t="s">
+      <c r="A83" s="73" t="s">
         <v>573</v>
       </c>
-      <c r="B83" s="83"/>
-      <c r="C83" s="83"/>
+      <c r="B83" s="73"/>
+      <c r="C83" s="73"/>
     </row>
     <row r="84" spans="1:3">
       <c r="A84" s="41" t="s">
@@ -9994,10 +10144,10 @@
       </c>
     </row>
     <row r="147" spans="1:3" ht="64.5" customHeight="1">
-      <c r="A147" s="80" t="s">
+      <c r="A147" s="75" t="s">
         <v>658</v>
       </c>
-      <c r="B147" s="81"/>
+      <c r="B147" s="76"/>
       <c r="C147" s="26" t="s">
         <v>292</v>
       </c>
@@ -10369,82 +10519,82 @@
       <c r="A197" s="24" t="s">
         <v>625</v>
       </c>
-      <c r="B197" s="75" t="s">
+      <c r="B197" s="74" t="s">
         <v>626</v>
       </c>
-      <c r="C197" s="75"/>
+      <c r="C197" s="74"/>
     </row>
     <row r="198" spans="1:3" ht="15.75">
       <c r="A198" s="24" t="s">
         <v>358</v>
       </c>
-      <c r="B198" s="75" t="s">
+      <c r="B198" s="74" t="s">
         <v>627</v>
       </c>
-      <c r="C198" s="75"/>
+      <c r="C198" s="74"/>
     </row>
     <row r="199" spans="1:3" ht="15.75">
       <c r="A199" s="24" t="s">
         <v>628</v>
       </c>
-      <c r="B199" s="75" t="s">
+      <c r="B199" s="74" t="s">
         <v>629</v>
       </c>
-      <c r="C199" s="75"/>
+      <c r="C199" s="74"/>
     </row>
     <row r="200" spans="1:3" ht="15.75">
       <c r="A200" s="24" t="s">
         <v>630</v>
       </c>
-      <c r="B200" s="75" t="s">
+      <c r="B200" s="74" t="s">
         <v>631</v>
       </c>
-      <c r="C200" s="75"/>
+      <c r="C200" s="74"/>
     </row>
     <row r="201" spans="1:3" ht="15.75">
       <c r="A201" s="24" t="s">
         <v>632</v>
       </c>
-      <c r="B201" s="75" t="s">
+      <c r="B201" s="74" t="s">
         <v>633</v>
       </c>
-      <c r="C201" s="75"/>
+      <c r="C201" s="74"/>
     </row>
     <row r="202" spans="1:3" ht="15.75">
       <c r="A202" s="24" t="s">
         <v>634</v>
       </c>
-      <c r="B202" s="75" t="s">
+      <c r="B202" s="74" t="s">
         <v>635</v>
       </c>
-      <c r="C202" s="75"/>
+      <c r="C202" s="74"/>
     </row>
     <row r="203" spans="1:3" ht="15.75">
       <c r="A203" s="24" t="s">
         <v>636</v>
       </c>
-      <c r="B203" s="75" t="s">
+      <c r="B203" s="74" t="s">
         <v>637</v>
       </c>
-      <c r="C203" s="75"/>
+      <c r="C203" s="74"/>
     </row>
     <row r="204" spans="1:3" ht="15.75">
       <c r="A204" s="24" t="s">
         <v>638</v>
       </c>
-      <c r="B204" s="75" t="s">
+      <c r="B204" s="74" t="s">
         <v>639</v>
       </c>
-      <c r="C204" s="75"/>
+      <c r="C204" s="74"/>
     </row>
     <row r="205" spans="1:3" ht="15.75">
       <c r="A205" s="24" t="s">
         <v>640</v>
       </c>
-      <c r="B205" s="75" t="s">
+      <c r="B205" s="74" t="s">
         <v>641</v>
       </c>
-      <c r="C205" s="75"/>
+      <c r="C205" s="74"/>
     </row>
     <row r="206" spans="1:3" ht="15.75">
       <c r="A206" s="33" t="s">
@@ -10454,66 +10604,66 @@
       <c r="C206" s="34"/>
     </row>
     <row r="207" spans="1:3" ht="15.75">
-      <c r="A207" s="73" t="s">
+      <c r="A207" s="79" t="s">
         <v>643</v>
       </c>
-      <c r="B207" s="74"/>
+      <c r="B207" s="80"/>
       <c r="C207" s="34"/>
     </row>
     <row r="208" spans="1:3" ht="15.75">
-      <c r="A208" s="73" t="s">
+      <c r="A208" s="79" t="s">
         <v>644</v>
       </c>
-      <c r="B208" s="74"/>
+      <c r="B208" s="80"/>
       <c r="C208" s="34"/>
     </row>
     <row r="209" spans="1:3" ht="15.75">
-      <c r="A209" s="73" t="s">
+      <c r="A209" s="79" t="s">
         <v>645</v>
       </c>
-      <c r="B209" s="74"/>
+      <c r="B209" s="80"/>
       <c r="C209" s="34"/>
     </row>
     <row r="210" spans="1:3" ht="15.75">
-      <c r="A210" s="73" t="s">
+      <c r="A210" s="79" t="s">
         <v>646</v>
       </c>
-      <c r="B210" s="74"/>
+      <c r="B210" s="80"/>
       <c r="C210" s="34"/>
     </row>
     <row r="211" spans="1:3" ht="15.75">
-      <c r="A211" s="73" t="s">
+      <c r="A211" s="79" t="s">
         <v>647</v>
       </c>
-      <c r="B211" s="74"/>
+      <c r="B211" s="80"/>
       <c r="C211" s="34"/>
     </row>
     <row r="212" spans="1:3" ht="15.75">
-      <c r="A212" s="73" t="s">
+      <c r="A212" s="79" t="s">
         <v>648</v>
       </c>
-      <c r="B212" s="74"/>
+      <c r="B212" s="80"/>
       <c r="C212" s="34"/>
     </row>
     <row r="213" spans="1:3" ht="15.75">
-      <c r="A213" s="73" t="s">
+      <c r="A213" s="79" t="s">
         <v>649</v>
       </c>
-      <c r="B213" s="74"/>
+      <c r="B213" s="80"/>
       <c r="C213" s="34"/>
     </row>
     <row r="214" spans="1:3" ht="15.75">
-      <c r="A214" s="73" t="s">
+      <c r="A214" s="79" t="s">
         <v>650</v>
       </c>
-      <c r="B214" s="74"/>
+      <c r="B214" s="80"/>
       <c r="C214" s="34"/>
     </row>
     <row r="215" spans="1:3" ht="15.75">
-      <c r="A215" s="73" t="s">
+      <c r="A215" s="79" t="s">
         <v>651</v>
       </c>
-      <c r="B215" s="74"/>
+      <c r="B215" s="80"/>
       <c r="C215" s="34"/>
     </row>
     <row r="216" spans="1:3">
@@ -10722,11 +10872,11 @@
       </c>
     </row>
     <row r="244" spans="1:3">
-      <c r="A244" s="76" t="s">
+      <c r="A244" s="78" t="s">
         <v>420</v>
       </c>
-      <c r="B244" s="76"/>
-      <c r="C244" s="76"/>
+      <c r="B244" s="78"/>
+      <c r="C244" s="78"/>
     </row>
     <row r="245" spans="1:3">
       <c r="A245" s="20" t="s">
@@ -10811,10 +10961,10 @@
       </c>
     </row>
     <row r="258" spans="1:3" ht="74.25" customHeight="1">
-      <c r="A258" s="82" t="s">
+      <c r="A258" s="77" t="s">
         <v>802</v>
       </c>
-      <c r="B258" s="82"/>
+      <c r="B258" s="77"/>
     </row>
     <row r="259" spans="1:3" ht="15.75">
       <c r="A259" s="49" t="s">
@@ -10823,12 +10973,23 @@
     </row>
   </sheetData>
   <mergeCells count="39">
-    <mergeCell ref="A76:B76"/>
-    <mergeCell ref="A78:C78"/>
-    <mergeCell ref="A83:C83"/>
-    <mergeCell ref="A94:C94"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="A56:C56"/>
+    <mergeCell ref="A208:B208"/>
+    <mergeCell ref="A207:B207"/>
+    <mergeCell ref="A209:B209"/>
+    <mergeCell ref="B203:C203"/>
+    <mergeCell ref="A215:B215"/>
+    <mergeCell ref="A214:B214"/>
+    <mergeCell ref="A213:B213"/>
+    <mergeCell ref="A212:B212"/>
+    <mergeCell ref="A211:B211"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="A17:C17"/>
     <mergeCell ref="A126:C126"/>
     <mergeCell ref="B197:C197"/>
     <mergeCell ref="B198:C198"/>
@@ -10845,23 +11006,12 @@
     <mergeCell ref="B201:C201"/>
     <mergeCell ref="B200:C200"/>
     <mergeCell ref="B199:C199"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="A33:C33"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="A208:B208"/>
-    <mergeCell ref="A207:B207"/>
-    <mergeCell ref="A209:B209"/>
-    <mergeCell ref="B203:C203"/>
-    <mergeCell ref="A215:B215"/>
-    <mergeCell ref="A214:B214"/>
-    <mergeCell ref="A213:B213"/>
-    <mergeCell ref="A212:B212"/>
-    <mergeCell ref="A211:B211"/>
+    <mergeCell ref="A76:B76"/>
+    <mergeCell ref="A78:C78"/>
+    <mergeCell ref="A83:C83"/>
+    <mergeCell ref="A94:C94"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="A56:C56"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
@@ -10870,7 +11020,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C177"/>
+  <dimension ref="A1:C188"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="33.42578125" style="50" customWidth="1"/>
@@ -10880,11 +11030,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="86" t="s">
+      <c r="A1" s="90" t="s">
         <v>720</v>
       </c>
-      <c r="B1" s="86"/>
-      <c r="C1" s="86"/>
+      <c r="B1" s="90"/>
+      <c r="C1" s="90"/>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="50" t="s">
@@ -11029,11 +11179,11 @@
       </c>
     </row>
     <row r="18" spans="1:3">
-      <c r="A18" s="86" t="s">
+      <c r="A18" s="90" t="s">
         <v>761</v>
       </c>
-      <c r="B18" s="86"/>
-      <c r="C18" s="86"/>
+      <c r="B18" s="90"/>
+      <c r="C18" s="90"/>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="50" t="s">
@@ -11091,11 +11241,11 @@
       </c>
     </row>
     <row r="24" spans="1:3">
-      <c r="A24" s="86" t="s">
+      <c r="A24" s="90" t="s">
         <v>756</v>
       </c>
-      <c r="B24" s="86"/>
-      <c r="C24" s="86"/>
+      <c r="B24" s="90"/>
+      <c r="C24" s="90"/>
     </row>
     <row r="25" spans="1:3" ht="30">
       <c r="A25" s="52" t="s">
@@ -11141,11 +11291,11 @@
       </c>
     </row>
     <row r="31" spans="1:3">
-      <c r="A31" s="86" t="s">
+      <c r="A31" s="90" t="s">
         <v>776</v>
       </c>
-      <c r="B31" s="86"/>
-      <c r="C31" s="86"/>
+      <c r="B31" s="90"/>
+      <c r="C31" s="90"/>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="50" t="s">
@@ -11212,11 +11362,11 @@
       </c>
     </row>
     <row r="42" spans="1:3" ht="18.75">
-      <c r="A42" s="94" t="s">
+      <c r="A42" s="87" t="s">
         <v>904</v>
       </c>
-      <c r="B42" s="94"/>
-      <c r="C42" s="94"/>
+      <c r="B42" s="87"/>
+      <c r="C42" s="87"/>
     </row>
     <row r="43" spans="1:3" ht="45">
       <c r="A43" s="55" t="s">
@@ -11301,11 +11451,11 @@
       <c r="C50" s="59"/>
     </row>
     <row r="51" spans="1:3" ht="18.75">
-      <c r="A51" s="90" t="s">
+      <c r="A51" s="89" t="s">
         <v>871</v>
       </c>
-      <c r="B51" s="90"/>
-      <c r="C51" s="90"/>
+      <c r="B51" s="89"/>
+      <c r="C51" s="89"/>
     </row>
     <row r="52" spans="1:3" ht="18.75">
       <c r="A52" s="92" t="s">
@@ -11517,11 +11667,11 @@
       </c>
     </row>
     <row r="73" spans="1:3">
-      <c r="A73" s="84" t="s">
+      <c r="A73" s="88" t="s">
         <v>1079</v>
       </c>
-      <c r="B73" s="84"/>
-      <c r="C73" s="84"/>
+      <c r="B73" s="88"/>
+      <c r="C73" s="88"/>
     </row>
     <row r="74" spans="1:3" ht="35.25" customHeight="1">
       <c r="A74" s="53" t="s">
@@ -11597,11 +11747,11 @@
       <c r="C82" s="59"/>
     </row>
     <row r="83" spans="1:3" ht="18.75">
-      <c r="A83" s="90" t="s">
+      <c r="A83" s="89" t="s">
         <v>837</v>
       </c>
-      <c r="B83" s="90"/>
-      <c r="C83" s="90"/>
+      <c r="B83" s="89"/>
+      <c r="C83" s="89"/>
     </row>
     <row r="84" spans="1:3" ht="75">
       <c r="A84" s="53" t="s">
@@ -11681,11 +11831,11 @@
       </c>
     </row>
     <row r="91" spans="1:3" ht="18.75">
-      <c r="A91" s="90" t="s">
+      <c r="A91" s="89" t="s">
         <v>927</v>
       </c>
-      <c r="B91" s="90"/>
-      <c r="C91" s="90"/>
+      <c r="B91" s="89"/>
+      <c r="C91" s="89"/>
     </row>
     <row r="92" spans="1:3" ht="45">
       <c r="A92" s="53" t="s">
@@ -11952,11 +12102,11 @@
       </c>
     </row>
     <row r="117" spans="1:3" ht="18.75">
-      <c r="A117" s="90" t="s">
+      <c r="A117" s="89" t="s">
         <v>976</v>
       </c>
-      <c r="B117" s="90"/>
-      <c r="C117" s="90"/>
+      <c r="B117" s="89"/>
+      <c r="C117" s="89"/>
     </row>
     <row r="118" spans="1:3" ht="30">
       <c r="A118" s="53" t="s">
@@ -11981,540 +12131,655 @@
       </c>
     </row>
     <row r="120" spans="1:3">
-      <c r="A120" s="59"/>
-      <c r="B120" s="59"/>
-      <c r="C120" s="59"/>
-    </row>
-    <row r="121" spans="1:3" ht="18.75">
-      <c r="A121" s="90" t="s">
+      <c r="A120" s="53" t="s">
+        <v>1136</v>
+      </c>
+      <c r="B120" s="53" t="s">
+        <v>1138</v>
+      </c>
+      <c r="C120" s="53" t="s">
+        <v>1137</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" ht="60">
+      <c r="A121" s="53" t="s">
+        <v>1140</v>
+      </c>
+      <c r="B121" s="53" t="s">
+        <v>1139</v>
+      </c>
+      <c r="C121" s="53" t="s">
+        <v>1141</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" ht="30">
+      <c r="A122" s="53" t="s">
+        <v>1142</v>
+      </c>
+      <c r="B122" s="53" t="s">
+        <v>1143</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" ht="60">
+      <c r="A123" s="53" t="s">
+        <v>1144</v>
+      </c>
+      <c r="B123" s="53" t="s">
+        <v>1147</v>
+      </c>
+      <c r="C123" s="53" t="s">
+        <v>1145</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" ht="60">
+      <c r="A124" s="53" t="s">
+        <v>1146</v>
+      </c>
+      <c r="B124" s="53" t="s">
+        <v>1148</v>
+      </c>
+      <c r="C124" s="53" t="s">
+        <v>1149</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3">
+      <c r="A125" s="59"/>
+      <c r="B125" s="59"/>
+      <c r="C125" s="59"/>
+    </row>
+    <row r="126" spans="1:3" ht="18.75">
+      <c r="A126" s="89" t="s">
         <v>977</v>
       </c>
-      <c r="B121" s="90"/>
-      <c r="C121" s="90"/>
-    </row>
-    <row r="122" spans="1:3" ht="33.75" customHeight="1">
-      <c r="A122" s="53" t="s">
+      <c r="B126" s="89"/>
+      <c r="C126" s="89"/>
+    </row>
+    <row r="127" spans="1:3" ht="33.75" customHeight="1">
+      <c r="A127" s="53" t="s">
         <v>975</v>
       </c>
-      <c r="B122" s="53" t="s">
+      <c r="B127" s="53" t="s">
         <v>979</v>
       </c>
-      <c r="C122" s="53" t="s">
+      <c r="C127" s="53" t="s">
         <v>978</v>
       </c>
     </row>
-    <row r="123" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A123" s="53" t="s">
+    <row r="128" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A128" s="53" t="s">
         <v>981</v>
       </c>
-      <c r="B123" s="53" t="s">
+      <c r="B128" s="53" t="s">
         <v>982</v>
       </c>
-      <c r="C123" s="53" t="s">
+      <c r="C128" s="53" t="s">
         <v>980</v>
       </c>
     </row>
-    <row r="124" spans="1:3" ht="30">
-      <c r="A124" s="57" t="s">
+    <row r="129" spans="1:3" ht="30">
+      <c r="A129" s="57" t="s">
         <v>983</v>
       </c>
-      <c r="B124" s="57" t="s">
+      <c r="B129" s="57" t="s">
         <v>984</v>
       </c>
-      <c r="C124" s="57" t="s">
+      <c r="C129" s="57" t="s">
         <v>985</v>
       </c>
     </row>
-    <row r="125" spans="1:3">
-      <c r="A125" s="60"/>
-      <c r="B125" s="60"/>
-      <c r="C125" s="60"/>
-    </row>
-    <row r="126" spans="1:3" ht="18.75">
-      <c r="A126" s="94" t="s">
+    <row r="130" spans="1:3">
+      <c r="A130" s="60"/>
+      <c r="B130" s="60"/>
+      <c r="C130" s="60"/>
+    </row>
+    <row r="131" spans="1:3" ht="18.75">
+      <c r="A131" s="87" t="s">
         <v>1017</v>
       </c>
-      <c r="B126" s="94"/>
-      <c r="C126" s="94"/>
-    </row>
-    <row r="127" spans="1:3" ht="45">
-      <c r="A127" s="53" t="s">
+      <c r="B131" s="87"/>
+      <c r="C131" s="87"/>
+    </row>
+    <row r="132" spans="1:3" ht="45">
+      <c r="A132" s="53" t="s">
         <v>986</v>
       </c>
-      <c r="B127" s="53" t="s">
+      <c r="B132" s="53" t="s">
         <v>988</v>
       </c>
-      <c r="C127" s="53" t="s">
+      <c r="C132" s="53" t="s">
         <v>992</v>
       </c>
     </row>
-    <row r="128" spans="1:3" ht="30">
-      <c r="A128" s="53" t="s">
+    <row r="133" spans="1:3" ht="30">
+      <c r="A133" s="53" t="s">
         <v>987</v>
       </c>
-      <c r="B128" s="53" t="s">
+      <c r="B133" s="53" t="s">
         <v>989</v>
       </c>
-      <c r="C128" s="53" t="s">
+      <c r="C133" s="53" t="s">
         <v>990</v>
       </c>
     </row>
-    <row r="129" spans="1:3" ht="75" customHeight="1">
-      <c r="A129" s="53" t="s">
+    <row r="134" spans="1:3" ht="75" customHeight="1">
+      <c r="A134" s="53" t="s">
         <v>991</v>
       </c>
-      <c r="B129" s="53" t="s">
+      <c r="B134" s="53" t="s">
         <v>993</v>
       </c>
-      <c r="C129" s="53" t="s">
+      <c r="C134" s="53" t="s">
         <v>994</v>
       </c>
     </row>
-    <row r="130" spans="1:3" ht="60" customHeight="1">
-      <c r="A130" s="57" t="s">
+    <row r="135" spans="1:3" ht="60" customHeight="1">
+      <c r="A135" s="57" t="s">
         <v>995</v>
       </c>
-      <c r="B130" s="57" t="s">
+      <c r="B135" s="57" t="s">
         <v>996</v>
       </c>
-      <c r="C130" s="95" t="s">
+      <c r="C135" s="84" t="s">
         <v>1001</v>
       </c>
     </row>
-    <row r="131" spans="1:3">
-      <c r="A131" s="62" t="s">
+    <row r="136" spans="1:3">
+      <c r="A136" s="62" t="s">
         <v>997</v>
       </c>
-      <c r="B131" s="64" t="s">
+      <c r="B136" s="64" t="s">
         <v>998</v>
       </c>
-      <c r="C131" s="96"/>
-    </row>
-    <row r="132" spans="1:3">
-      <c r="A132" s="63" t="s">
+      <c r="C136" s="85"/>
+    </row>
+    <row r="137" spans="1:3">
+      <c r="A137" s="63" t="s">
         <v>999</v>
       </c>
-      <c r="B132" s="65" t="s">
+      <c r="B137" s="65" t="s">
         <v>1000</v>
       </c>
-      <c r="C132" s="97"/>
-    </row>
-    <row r="133" spans="1:3" ht="45">
-      <c r="A133" s="53" t="s">
+      <c r="C137" s="86"/>
+    </row>
+    <row r="138" spans="1:3" ht="45">
+      <c r="A138" s="53" t="s">
         <v>1002</v>
       </c>
-      <c r="B133" s="53" t="s">
+      <c r="B138" s="53" t="s">
         <v>1004</v>
       </c>
-      <c r="C133" s="53" t="s">
+      <c r="C138" s="53" t="s">
         <v>1003</v>
       </c>
     </row>
-    <row r="134" spans="1:3" ht="47.25" customHeight="1">
-      <c r="A134" s="53" t="s">
+    <row r="139" spans="1:3" ht="47.25" customHeight="1">
+      <c r="A139" s="53" t="s">
         <v>1005</v>
       </c>
-      <c r="B134" s="53" t="s">
+      <c r="B139" s="53" t="s">
         <v>1006</v>
       </c>
-      <c r="C134" s="53" t="s">
+      <c r="C139" s="53" t="s">
         <v>1007</v>
       </c>
     </row>
-    <row r="135" spans="1:3" ht="45">
-      <c r="A135" s="53" t="s">
+    <row r="140" spans="1:3" ht="45">
+      <c r="A140" s="53" t="s">
         <v>1008</v>
       </c>
-      <c r="B135" s="53" t="s">
+      <c r="B140" s="53" t="s">
         <v>1010</v>
       </c>
-      <c r="C135" s="53" t="s">
+      <c r="C140" s="53" t="s">
         <v>1009</v>
       </c>
     </row>
-    <row r="136" spans="1:3" ht="52.5" customHeight="1">
-      <c r="A136" s="53" t="s">
+    <row r="141" spans="1:3" ht="52.5" customHeight="1">
+      <c r="A141" s="53" t="s">
         <v>1011</v>
       </c>
-      <c r="B136" s="53" t="s">
+      <c r="B141" s="53" t="s">
         <v>1013</v>
       </c>
-      <c r="C136" s="53" t="s">
+      <c r="C141" s="53" t="s">
         <v>1012</v>
       </c>
     </row>
-    <row r="137" spans="1:3" ht="50.25" customHeight="1">
-      <c r="A137" s="53" t="s">
+    <row r="142" spans="1:3" ht="50.25" customHeight="1">
+      <c r="A142" s="53" t="s">
         <v>1014</v>
       </c>
-      <c r="B137" s="53" t="s">
+      <c r="B142" s="53" t="s">
         <v>1015</v>
       </c>
-      <c r="C137" s="53" t="s">
+      <c r="C142" s="53" t="s">
         <v>1016</v>
       </c>
     </row>
-    <row r="138" spans="1:3">
-      <c r="A138" s="84" t="s">
+    <row r="143" spans="1:3">
+      <c r="A143" s="88" t="s">
         <v>1018</v>
       </c>
-      <c r="B138" s="84"/>
-      <c r="C138" s="84"/>
-    </row>
-    <row r="139" spans="1:3" ht="46.5" customHeight="1">
-      <c r="A139" s="53" t="s">
+      <c r="B143" s="88"/>
+      <c r="C143" s="88"/>
+    </row>
+    <row r="144" spans="1:3" ht="46.5" customHeight="1">
+      <c r="A144" s="53" t="s">
         <v>1027</v>
       </c>
-      <c r="B139" s="53" t="s">
+      <c r="B144" s="53" t="s">
         <v>1020</v>
       </c>
-      <c r="C139" s="53" t="s">
+      <c r="C144" s="53" t="s">
         <v>1019</v>
       </c>
     </row>
-    <row r="140" spans="1:3" ht="30">
-      <c r="A140" s="53" t="s">
+    <row r="145" spans="1:3" ht="30">
+      <c r="A145" s="53" t="s">
         <v>1028</v>
       </c>
-      <c r="B140" s="53" t="s">
+      <c r="B145" s="53" t="s">
         <v>1022</v>
       </c>
-      <c r="C140" s="53" t="s">
+      <c r="C145" s="53" t="s">
         <v>1021</v>
       </c>
     </row>
-    <row r="141" spans="1:3" ht="30">
-      <c r="A141" s="53" t="s">
+    <row r="146" spans="1:3" ht="30">
+      <c r="A146" s="53" t="s">
         <v>1029</v>
       </c>
-      <c r="B141" s="53" t="s">
+      <c r="B146" s="53" t="s">
         <v>1024</v>
       </c>
-      <c r="C141" s="53" t="s">
+      <c r="C146" s="53" t="s">
         <v>1023</v>
       </c>
     </row>
-    <row r="142" spans="1:3" ht="30">
-      <c r="A142" s="53" t="s">
+    <row r="147" spans="1:3" ht="30">
+      <c r="A147" s="53" t="s">
         <v>1030</v>
       </c>
-      <c r="B142" s="53" t="s">
+      <c r="B147" s="53" t="s">
         <v>1025</v>
       </c>
-      <c r="C142" s="53" t="s">
+      <c r="C147" s="53" t="s">
         <v>1026</v>
       </c>
     </row>
-    <row r="143" spans="1:3">
-      <c r="A143" s="84" t="s">
+    <row r="148" spans="1:3">
+      <c r="A148" s="88" t="s">
         <v>1031</v>
       </c>
-      <c r="B143" s="84"/>
-      <c r="C143" s="84"/>
-    </row>
-    <row r="144" spans="1:3" ht="62.25" customHeight="1">
-      <c r="A144" s="53" t="s">
+      <c r="B148" s="88"/>
+      <c r="C148" s="88"/>
+    </row>
+    <row r="149" spans="1:3" ht="62.25" customHeight="1">
+      <c r="A149" s="53" t="s">
         <v>1032</v>
       </c>
-      <c r="B144" s="53" t="s">
+      <c r="B149" s="53" t="s">
         <v>1035</v>
       </c>
-      <c r="C144" s="53" t="s">
+      <c r="C149" s="53" t="s">
         <v>1033</v>
       </c>
     </row>
-    <row r="145" spans="1:3" ht="60">
-      <c r="A145" s="53" t="s">
+    <row r="150" spans="1:3" ht="60">
+      <c r="A150" s="53" t="s">
         <v>1032</v>
       </c>
-      <c r="B145" s="53" t="s">
+      <c r="B150" s="53" t="s">
         <v>1034</v>
       </c>
-      <c r="C145" s="53" t="s">
+      <c r="C150" s="53" t="s">
         <v>1036</v>
       </c>
     </row>
-    <row r="147" spans="1:3" ht="45">
-      <c r="A147" s="53" t="s">
+    <row r="152" spans="1:3" ht="45">
+      <c r="A152" s="53" t="s">
         <v>1037</v>
       </c>
-      <c r="B147" s="53" t="s">
+      <c r="B152" s="53" t="s">
         <v>1046</v>
       </c>
-      <c r="C147" s="53" t="s">
+      <c r="C152" s="53" t="s">
         <v>1038</v>
       </c>
     </row>
-    <row r="148" spans="1:3" ht="45">
-      <c r="A148" s="53" t="s">
+    <row r="153" spans="1:3" ht="45">
+      <c r="A153" s="53" t="s">
         <v>1039</v>
       </c>
-      <c r="B148" s="53" t="s">
+      <c r="B153" s="53" t="s">
         <v>1047</v>
       </c>
-      <c r="C148" s="53" t="s">
+      <c r="C153" s="53" t="s">
         <v>1041</v>
       </c>
     </row>
-    <row r="149" spans="1:3" ht="45">
-      <c r="A149" s="53" t="s">
+    <row r="154" spans="1:3" ht="45">
+      <c r="A154" s="53" t="s">
         <v>1040</v>
       </c>
-      <c r="B149" s="53" t="s">
+      <c r="B154" s="53" t="s">
         <v>1048</v>
       </c>
-      <c r="C149" s="53" t="s">
+      <c r="C154" s="53" t="s">
         <v>1042</v>
       </c>
     </row>
-    <row r="150" spans="1:3" ht="45">
-      <c r="A150" s="53" t="s">
+    <row r="155" spans="1:3" ht="45">
+      <c r="A155" s="53" t="s">
         <v>1043</v>
       </c>
-      <c r="B150" s="53" t="s">
+      <c r="B155" s="53" t="s">
         <v>1045</v>
       </c>
-      <c r="C150" s="53" t="s">
+      <c r="C155" s="53" t="s">
         <v>1044</v>
       </c>
     </row>
-    <row r="151" spans="1:3" ht="15" customHeight="1"/>
-    <row r="152" spans="1:3" ht="30">
-      <c r="A152" s="85" t="s">
+    <row r="156" spans="1:3" ht="15" customHeight="1"/>
+    <row r="157" spans="1:3" ht="30">
+      <c r="A157" s="95" t="s">
         <v>1049</v>
       </c>
-      <c r="B152" s="53" t="s">
+      <c r="B157" s="53" t="s">
         <v>1050</v>
       </c>
-      <c r="C152" s="53" t="s">
+      <c r="C157" s="53" t="s">
         <v>1051</v>
       </c>
     </row>
-    <row r="153" spans="1:3" ht="45">
-      <c r="A153" s="85"/>
-      <c r="B153" s="53" t="s">
+    <row r="158" spans="1:3" ht="45">
+      <c r="A158" s="95"/>
+      <c r="B158" s="53" t="s">
         <v>1052</v>
       </c>
-      <c r="C153" s="53" t="s">
+      <c r="C158" s="53" t="s">
         <v>1053</v>
       </c>
     </row>
-    <row r="154" spans="1:3" ht="15" customHeight="1"/>
-    <row r="155" spans="1:3" ht="60">
-      <c r="A155" s="53" t="s">
+    <row r="159" spans="1:3" ht="15" customHeight="1"/>
+    <row r="160" spans="1:3" ht="60">
+      <c r="A160" s="53" t="s">
         <v>1054</v>
       </c>
-      <c r="B155" s="53" t="s">
+      <c r="B160" s="53" t="s">
         <v>1055</v>
       </c>
-      <c r="C155" s="87" t="s">
+      <c r="C160" s="96" t="s">
         <v>1067</v>
       </c>
     </row>
-    <row r="156" spans="1:3" ht="60">
-      <c r="A156" s="53" t="s">
+    <row r="161" spans="1:3" ht="60">
+      <c r="A161" s="53" t="s">
         <v>1056</v>
       </c>
-      <c r="B156" s="53" t="s">
+      <c r="B161" s="53" t="s">
         <v>1057</v>
       </c>
-      <c r="C156" s="89"/>
-    </row>
-    <row r="157" spans="1:3" ht="15" customHeight="1">
-      <c r="A157" s="86" t="s">
+      <c r="C161" s="98"/>
+    </row>
+    <row r="162" spans="1:3" ht="15" customHeight="1">
+      <c r="A162" s="90" t="s">
         <v>1058</v>
       </c>
-      <c r="B157" s="86"/>
-      <c r="C157" s="86"/>
-    </row>
-    <row r="158" spans="1:3" ht="30">
-      <c r="A158" s="57" t="s">
+      <c r="B162" s="90"/>
+      <c r="C162" s="90"/>
+    </row>
+    <row r="163" spans="1:3" ht="30">
+      <c r="A163" s="57" t="s">
         <v>1068</v>
       </c>
-      <c r="B158" s="57" t="s">
+      <c r="B163" s="57" t="s">
         <v>1062</v>
       </c>
-      <c r="C158" s="87" t="s">
+      <c r="C163" s="96" t="s">
         <v>1059</v>
       </c>
     </row>
-    <row r="159" spans="1:3">
-      <c r="A159" s="53" t="s">
+    <row r="164" spans="1:3">
+      <c r="A164" s="53" t="s">
         <v>1060</v>
       </c>
-      <c r="B159" s="53" t="s">
+      <c r="B164" s="53" t="s">
         <v>1061</v>
       </c>
-      <c r="C159" s="88"/>
-    </row>
-    <row r="160" spans="1:3">
-      <c r="A160" s="66" t="s">
+      <c r="C164" s="97"/>
+    </row>
+    <row r="165" spans="1:3">
+      <c r="A165" s="66" t="s">
         <v>1064</v>
       </c>
-      <c r="B160" s="53" t="s">
+      <c r="B165" s="53" t="s">
         <v>1063</v>
       </c>
-      <c r="C160" s="88"/>
-    </row>
-    <row r="161" spans="1:3" ht="30">
-      <c r="A161" s="53" t="s">
+      <c r="C165" s="97"/>
+    </row>
+    <row r="166" spans="1:3" ht="30">
+      <c r="A166" s="53" t="s">
         <v>1065</v>
       </c>
-      <c r="B161" s="53" t="s">
+      <c r="B166" s="53" t="s">
         <v>1066</v>
       </c>
-      <c r="C161" s="89"/>
-    </row>
-    <row r="162" spans="1:3" ht="45">
-      <c r="A162" s="53" t="s">
+      <c r="C166" s="98"/>
+    </row>
+    <row r="167" spans="1:3" ht="45">
+      <c r="A167" s="53" t="s">
         <v>1069</v>
       </c>
-      <c r="B162" s="53"/>
-      <c r="C162" s="53" t="s">
+      <c r="B167" s="53"/>
+      <c r="C167" s="53" t="s">
         <v>1070</v>
       </c>
     </row>
-    <row r="163" spans="1:3">
-      <c r="A163" s="84" t="s">
+    <row r="168" spans="1:3">
+      <c r="A168" s="88" t="s">
         <v>1071</v>
       </c>
-      <c r="B163" s="84"/>
-      <c r="C163" s="84"/>
-    </row>
-    <row r="164" spans="1:3" ht="51.75" customHeight="1">
-      <c r="A164" s="53" t="s">
+      <c r="B168" s="88"/>
+      <c r="C168" s="88"/>
+    </row>
+    <row r="169" spans="1:3" ht="51.75" customHeight="1">
+      <c r="A169" s="53" t="s">
         <v>1072</v>
       </c>
-      <c r="B164" s="53" t="s">
+      <c r="B169" s="53" t="s">
         <v>1074</v>
       </c>
-      <c r="C164" s="75" t="s">
+      <c r="C169" s="74" t="s">
         <v>1076</v>
       </c>
     </row>
-    <row r="165" spans="1:3" ht="51.75" customHeight="1">
-      <c r="A165" s="53" t="s">
+    <row r="170" spans="1:3" ht="51.75" customHeight="1">
+      <c r="A170" s="53" t="s">
         <v>1073</v>
       </c>
-      <c r="B165" s="53" t="s">
+      <c r="B170" s="53" t="s">
         <v>1075</v>
       </c>
-      <c r="C165" s="75"/>
-    </row>
-    <row r="166" spans="1:3">
-      <c r="A166" s="84" t="s">
+      <c r="C170" s="74"/>
+    </row>
+    <row r="171" spans="1:3">
+      <c r="A171" s="88" t="s">
         <v>1094</v>
       </c>
-      <c r="B166" s="84"/>
-      <c r="C166" s="84"/>
-    </row>
-    <row r="167" spans="1:3" ht="60">
-      <c r="A167" s="53" t="s">
+      <c r="B171" s="88"/>
+      <c r="C171" s="88"/>
+    </row>
+    <row r="172" spans="1:3" ht="60">
+      <c r="A172" s="53" t="s">
         <v>1095</v>
       </c>
-      <c r="B167" s="53" t="s">
+      <c r="B172" s="53" t="s">
         <v>1097</v>
       </c>
-      <c r="C167" s="53" t="s">
+      <c r="C172" s="53" t="s">
         <v>1096</v>
       </c>
     </row>
-    <row r="168" spans="1:3" ht="60">
-      <c r="A168" s="53" t="s">
+    <row r="173" spans="1:3" ht="60">
+      <c r="A173" s="53" t="s">
         <v>1098</v>
       </c>
-      <c r="B168" s="53" t="s">
+      <c r="B173" s="53" t="s">
         <v>1099</v>
       </c>
-      <c r="C168" s="53" t="s">
+      <c r="C173" s="53" t="s">
         <v>1100</v>
       </c>
     </row>
-    <row r="169" spans="1:3" ht="45">
-      <c r="A169" s="53" t="s">
+    <row r="174" spans="1:3" ht="45">
+      <c r="A174" s="53" t="s">
         <v>1102</v>
       </c>
-      <c r="B169" s="53" t="s">
+      <c r="B174" s="53" t="s">
         <v>1103</v>
       </c>
-      <c r="C169" s="53" t="s">
+      <c r="C174" s="53" t="s">
         <v>1101</v>
       </c>
     </row>
-    <row r="170" spans="1:3" ht="30">
-      <c r="A170" s="53" t="s">
+    <row r="175" spans="1:3" ht="30">
+      <c r="A175" s="53" t="s">
         <v>1115</v>
       </c>
-      <c r="B170" s="53" t="s">
+      <c r="B175" s="53" t="s">
         <v>1116</v>
       </c>
-      <c r="C170" s="53"/>
-    </row>
-    <row r="171" spans="1:3" ht="30">
-      <c r="A171" s="53" t="s">
+      <c r="C175" s="53"/>
+    </row>
+    <row r="176" spans="1:3" ht="30">
+      <c r="A176" s="53" t="s">
         <v>1104</v>
       </c>
-      <c r="B171" s="53" t="s">
+      <c r="B176" s="53" t="s">
         <v>1106</v>
       </c>
-      <c r="C171" s="53"/>
-    </row>
-    <row r="172" spans="1:3" ht="51.75" customHeight="1">
-      <c r="A172" s="53" t="s">
+      <c r="C176" s="53"/>
+    </row>
+    <row r="177" spans="1:3" ht="51.75" customHeight="1">
+      <c r="A177" s="53" t="s">
         <v>1105</v>
       </c>
-      <c r="B172" s="53" t="s">
+      <c r="B177" s="53" t="s">
         <v>1107</v>
       </c>
-      <c r="C172" s="53"/>
-    </row>
-    <row r="173" spans="1:3" ht="45">
-      <c r="A173" s="53" t="s">
+      <c r="C177" s="53"/>
+    </row>
+    <row r="178" spans="1:3" ht="45">
+      <c r="A178" s="53" t="s">
         <v>1108</v>
       </c>
-      <c r="B173" s="53" t="s">
+      <c r="B178" s="53" t="s">
         <v>1109</v>
       </c>
-      <c r="C173" s="53" t="s">
+      <c r="C178" s="53" t="s">
         <v>1111</v>
       </c>
     </row>
-    <row r="174" spans="1:3" ht="30">
-      <c r="A174" s="53" t="s">
+    <row r="179" spans="1:3" ht="30">
+      <c r="A179" s="53" t="s">
         <v>298</v>
       </c>
-      <c r="B174" s="53" t="s">
+      <c r="B179" s="53" t="s">
         <v>1110</v>
       </c>
-      <c r="C174" s="53" t="s">
+      <c r="C179" s="53" t="s">
         <v>1112</v>
       </c>
     </row>
-    <row r="176" spans="1:3" ht="60">
-      <c r="A176" s="53" t="s">
+    <row r="181" spans="1:3" ht="60">
+      <c r="A181" s="53" t="s">
         <v>1117</v>
       </c>
-      <c r="B176" s="53" t="s">
+      <c r="B181" s="53" t="s">
         <v>1118</v>
       </c>
-      <c r="C176" s="53"/>
-    </row>
-    <row r="177" spans="1:3" ht="75">
-      <c r="A177" s="53" t="s">
+      <c r="C181" s="53"/>
+    </row>
+    <row r="182" spans="1:3" ht="75">
+      <c r="A182" s="53" t="s">
         <v>1119</v>
       </c>
-      <c r="B177" s="53" t="s">
+      <c r="B182" s="53" t="s">
         <v>1120</v>
       </c>
-      <c r="C177" s="53"/>
+      <c r="C182" s="53"/>
+    </row>
+    <row r="183" spans="1:3" ht="18.75">
+      <c r="A183" s="94" t="s">
+        <v>1125</v>
+      </c>
+      <c r="B183" s="94"/>
+      <c r="C183" s="94"/>
+    </row>
+    <row r="184" spans="1:3" ht="30">
+      <c r="A184" s="53" t="s">
+        <v>1121</v>
+      </c>
+      <c r="B184" s="53" t="s">
+        <v>1122</v>
+      </c>
+      <c r="C184" s="53"/>
+    </row>
+    <row r="185" spans="1:3" ht="44.25" customHeight="1">
+      <c r="A185" s="53" t="s">
+        <v>1135</v>
+      </c>
+      <c r="B185" s="53" t="s">
+        <v>1124</v>
+      </c>
+      <c r="C185" s="53" t="s">
+        <v>1123</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" ht="45">
+      <c r="A186" s="53" t="s">
+        <v>1126</v>
+      </c>
+      <c r="B186" s="53" t="s">
+        <v>1127</v>
+      </c>
+      <c r="C186" s="53" t="s">
+        <v>1128</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" ht="33" customHeight="1">
+      <c r="A187" s="53" t="s">
+        <v>1129</v>
+      </c>
+      <c r="B187" s="53" t="s">
+        <v>1130</v>
+      </c>
+      <c r="C187" s="53" t="s">
+        <v>1131</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" ht="60">
+      <c r="A188" s="53" t="s">
+        <v>1132</v>
+      </c>
+      <c r="B188" s="53" t="s">
+        <v>1133</v>
+      </c>
+      <c r="C188" s="53" t="s">
+        <v>1134</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="28">
-    <mergeCell ref="C130:C132"/>
-    <mergeCell ref="A126:C126"/>
-    <mergeCell ref="A138:C138"/>
-    <mergeCell ref="A143:C143"/>
-    <mergeCell ref="A121:C121"/>
+  <mergeCells count="29">
+    <mergeCell ref="A183:C183"/>
+    <mergeCell ref="A171:C171"/>
+    <mergeCell ref="C169:C170"/>
+    <mergeCell ref="A157:A158"/>
+    <mergeCell ref="A162:C162"/>
+    <mergeCell ref="C163:C166"/>
+    <mergeCell ref="C160:C161"/>
+    <mergeCell ref="A168:C168"/>
     <mergeCell ref="A117:C117"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A9:C9"/>
@@ -12531,13 +12796,11 @@
     <mergeCell ref="A69:C69"/>
     <mergeCell ref="A42:C42"/>
     <mergeCell ref="A73:C73"/>
-    <mergeCell ref="A166:C166"/>
-    <mergeCell ref="C164:C165"/>
-    <mergeCell ref="A152:A153"/>
-    <mergeCell ref="A157:C157"/>
-    <mergeCell ref="C158:C161"/>
-    <mergeCell ref="C155:C156"/>
-    <mergeCell ref="A163:C163"/>
+    <mergeCell ref="C135:C137"/>
+    <mergeCell ref="A131:C131"/>
+    <mergeCell ref="A143:C143"/>
+    <mergeCell ref="A148:C148"/>
+    <mergeCell ref="A126:C126"/>
   </mergeCells>
   <pageMargins left="0.15748031496062992" right="0.19685039370078741" top="0.23" bottom="0.17" header="0.22" footer="0.16"/>
   <pageSetup paperSize="9" orientation="landscape" verticalDpi="0" r:id="rId1"/>
